--- a/revise/output/tbl/月平均搭乘里程.xlsx
+++ b/revise/output/tbl/月平均搭乘里程.xlsx
@@ -449,13 +449,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>20148</v>
+        <v>20025</v>
       </c>
       <c r="C2" t="n">
-        <v>472248.51</v>
+        <v>471983.17</v>
       </c>
       <c r="D2" t="n">
-        <v>23.44</v>
+        <v>23.57</v>
       </c>
     </row>
     <row r="3">
@@ -463,13 +463,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>17815</v>
+        <v>17679</v>
       </c>
       <c r="C3" t="n">
-        <v>442019.68</v>
+        <v>441840.47</v>
       </c>
       <c r="D3" t="n">
-        <v>24.81</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="4">
@@ -477,13 +477,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>21281</v>
+        <v>21146</v>
       </c>
       <c r="C4" t="n">
-        <v>518463.04</v>
+        <v>518318.78</v>
       </c>
       <c r="D4" t="n">
-        <v>24.36</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="5">
@@ -491,13 +491,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>27316</v>
+        <v>27157</v>
       </c>
       <c r="C5" t="n">
-        <v>618841.35</v>
+        <v>618397.21</v>
       </c>
       <c r="D5" t="n">
-        <v>22.65</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="6">
@@ -505,13 +505,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>26316</v>
+        <v>26105</v>
       </c>
       <c r="C6" t="n">
-        <v>576184.23</v>
+        <v>575574.5</v>
       </c>
       <c r="D6" t="n">
-        <v>21.89</v>
+        <v>22.05</v>
       </c>
     </row>
     <row r="7">
@@ -519,13 +519,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>31473</v>
+        <v>31303</v>
       </c>
       <c r="C7" t="n">
-        <v>684867.3</v>
+        <v>684379.38</v>
       </c>
       <c r="D7" t="n">
-        <v>21.76</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="8">
@@ -533,13 +533,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>30475</v>
+        <v>30347</v>
       </c>
       <c r="C8" t="n">
-        <v>690502.63</v>
+        <v>690299.33</v>
       </c>
       <c r="D8" t="n">
-        <v>22.66</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="9">
@@ -547,13 +547,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>25166</v>
+        <v>24982</v>
       </c>
       <c r="C9" t="n">
-        <v>600512.36</v>
+        <v>600412.82</v>
       </c>
       <c r="D9" t="n">
-        <v>23.86</v>
+        <v>24.03</v>
       </c>
     </row>
     <row r="10">
@@ -561,13 +561,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>24705</v>
+        <v>24618</v>
       </c>
       <c r="C10" t="n">
-        <v>576830.08</v>
+        <v>576770.05</v>
       </c>
       <c r="D10" t="n">
-        <v>23.35</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="11">
@@ -575,13 +575,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>31259</v>
+        <v>31122</v>
       </c>
       <c r="C11" t="n">
-        <v>702123.45</v>
+        <v>701912.82</v>
       </c>
       <c r="D11" t="n">
-        <v>22.46</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="12">
@@ -589,13 +589,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>31398</v>
+        <v>31253</v>
       </c>
       <c r="C12" t="n">
-        <v>715689.54</v>
+        <v>715323.98</v>
       </c>
       <c r="D12" t="n">
-        <v>22.79</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="13">
@@ -603,13 +603,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="n">
-        <v>30858</v>
+        <v>30717</v>
       </c>
       <c r="C13" t="n">
-        <v>691473.35</v>
+        <v>691064.32</v>
       </c>
       <c r="D13" t="n">
-        <v>22.41</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="14">
@@ -617,13 +617,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="n">
-        <v>29024</v>
+        <v>28832</v>
       </c>
       <c r="C14" t="n">
-        <v>673117.28</v>
+        <v>672804.92</v>
       </c>
       <c r="D14" t="n">
-        <v>23.19</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="15">
@@ -631,13 +631,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="n">
-        <v>27565</v>
+        <v>27444</v>
       </c>
       <c r="C15" t="n">
-        <v>674283.24</v>
+        <v>673949.3</v>
       </c>
       <c r="D15" t="n">
-        <v>24.46</v>
+        <v>24.56</v>
       </c>
     </row>
     <row r="16">
@@ -645,13 +645,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="n">
-        <v>28361</v>
+        <v>28204</v>
       </c>
       <c r="C16" t="n">
-        <v>690004.4</v>
+        <v>689889.64</v>
       </c>
       <c r="D16" t="n">
-        <v>24.33</v>
+        <v>24.46</v>
       </c>
     </row>
     <row r="17">
@@ -659,13 +659,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="n">
-        <v>30017</v>
+        <v>29887</v>
       </c>
       <c r="C17" t="n">
-        <v>663350.28</v>
+        <v>663213.45</v>
       </c>
       <c r="D17" t="n">
-        <v>22.1</v>
+        <v>22.19</v>
       </c>
     </row>
     <row r="18">
@@ -673,13 +673,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="n">
-        <v>31643</v>
+        <v>31474</v>
       </c>
       <c r="C18" t="n">
-        <v>699973.73</v>
+        <v>699613.99</v>
       </c>
       <c r="D18" t="n">
-        <v>22.12</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="19">
@@ -687,13 +687,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="n">
-        <v>26103</v>
+        <v>25996</v>
       </c>
       <c r="C19" t="n">
-        <v>572540.82</v>
+        <v>572120.95</v>
       </c>
       <c r="D19" t="n">
-        <v>21.93</v>
+        <v>22.01</v>
       </c>
     </row>
     <row r="20">
@@ -701,13 +701,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="n">
-        <v>31444</v>
+        <v>31325</v>
       </c>
       <c r="C20" t="n">
-        <v>696248.21</v>
+        <v>696103.22</v>
       </c>
       <c r="D20" t="n">
-        <v>22.14</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="21">
@@ -715,13 +715,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="n">
-        <v>27594</v>
+        <v>27482</v>
       </c>
       <c r="C21" t="n">
-        <v>596669.23</v>
+        <v>596531.02</v>
       </c>
       <c r="D21" t="n">
-        <v>21.62</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="22">
@@ -729,13 +729,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="n">
-        <v>24146</v>
+        <v>24046</v>
       </c>
       <c r="C22" t="n">
-        <v>588594.05</v>
+        <v>588454.09</v>
       </c>
       <c r="D22" t="n">
-        <v>24.38</v>
+        <v>24.47</v>
       </c>
     </row>
     <row r="23">
@@ -743,13 +743,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="n">
-        <v>34104</v>
+        <v>33937</v>
       </c>
       <c r="C23" t="n">
-        <v>722973.07</v>
+        <v>722601.31</v>
       </c>
       <c r="D23" t="n">
-        <v>21.2</v>
+        <v>21.29</v>
       </c>
     </row>
     <row r="24">
@@ -757,13 +757,13 @@
         <v>26</v>
       </c>
       <c r="B24" t="n">
-        <v>34305</v>
+        <v>34118</v>
       </c>
       <c r="C24" t="n">
-        <v>759953.68</v>
+        <v>759112.97</v>
       </c>
       <c r="D24" t="n">
-        <v>22.15</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="25">
@@ -771,13 +771,13 @@
         <v>27</v>
       </c>
       <c r="B25" t="n">
-        <v>33146</v>
+        <v>32998</v>
       </c>
       <c r="C25" t="n">
-        <v>709815.24</v>
+        <v>709230.45</v>
       </c>
       <c r="D25" t="n">
-        <v>21.41</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="26">
@@ -785,13 +785,13 @@
         <v>28</v>
       </c>
       <c r="B26" t="n">
-        <v>29272</v>
+        <v>29129</v>
       </c>
       <c r="C26" t="n">
-        <v>648878.08</v>
+        <v>648560.44</v>
       </c>
       <c r="D26" t="n">
-        <v>22.17</v>
+        <v>22.27</v>
       </c>
     </row>
   </sheetData>
@@ -824,13 +824,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>67983</v>
+        <v>66725</v>
       </c>
       <c r="C2" t="n">
-        <v>1670074.69</v>
+        <v>1534898.93</v>
       </c>
       <c r="D2" t="n">
-        <v>24.57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -838,13 +838,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>57081</v>
+        <v>55132</v>
       </c>
       <c r="C3" t="n">
-        <v>1546221.78</v>
+        <v>1381813.75</v>
       </c>
       <c r="D3" t="n">
-        <v>27.09</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="4">
@@ -852,13 +852,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>69374</v>
+        <v>65318</v>
       </c>
       <c r="C4" t="n">
-        <v>2030384.59</v>
+        <v>1687869.73</v>
       </c>
       <c r="D4" t="n">
-        <v>29.27</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="5">
@@ -866,13 +866,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>84645</v>
+        <v>81392</v>
       </c>
       <c r="C5" t="n">
-        <v>2173361.08</v>
+        <v>1879076.79</v>
       </c>
       <c r="D5" t="n">
-        <v>25.68</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="6">
@@ -880,13 +880,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>76221</v>
+        <v>74347</v>
       </c>
       <c r="C6" t="n">
-        <v>1883685.61</v>
+        <v>1705157.98</v>
       </c>
       <c r="D6" t="n">
-        <v>24.71</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="7">
@@ -894,13 +894,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>89518</v>
+        <v>87269</v>
       </c>
       <c r="C7" t="n">
-        <v>2191622.76</v>
+        <v>1966514.84</v>
       </c>
       <c r="D7" t="n">
-        <v>24.48</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="8">
@@ -908,13 +908,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>91676</v>
+        <v>89434</v>
       </c>
       <c r="C8" t="n">
-        <v>2209412.76</v>
+        <v>1974535.12</v>
       </c>
       <c r="D8" t="n">
-        <v>24.1</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="9">
@@ -922,13 +922,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>70026</v>
+        <v>68917</v>
       </c>
       <c r="C9" t="n">
-        <v>1711481.55</v>
+        <v>1603869.73</v>
       </c>
       <c r="D9" t="n">
-        <v>24.44</v>
+        <v>23.27</v>
       </c>
     </row>
     <row r="10">
@@ -936,13 +936,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>66658</v>
+        <v>65427</v>
       </c>
       <c r="C10" t="n">
-        <v>1596588.13</v>
+        <v>1480269.72</v>
       </c>
       <c r="D10" t="n">
-        <v>23.95</v>
+        <v>22.62</v>
       </c>
     </row>
     <row r="11">
@@ -950,13 +950,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>84242</v>
+        <v>82874</v>
       </c>
       <c r="C11" t="n">
-        <v>1957734.55</v>
+        <v>1822418.22</v>
       </c>
       <c r="D11" t="n">
-        <v>23.24</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="12">
@@ -964,13 +964,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>81587</v>
+        <v>80386</v>
       </c>
       <c r="C12" t="n">
-        <v>1900692.48</v>
+        <v>1770192.41</v>
       </c>
       <c r="D12" t="n">
-        <v>23.3</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="13">
@@ -978,13 +978,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="n">
-        <v>80446</v>
+        <v>79392</v>
       </c>
       <c r="C13" t="n">
-        <v>1875427.35</v>
+        <v>1756858.22</v>
       </c>
       <c r="D13" t="n">
-        <v>23.31</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="14">
@@ -992,13 +992,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="n">
-        <v>75769</v>
+        <v>73723</v>
       </c>
       <c r="C14" t="n">
-        <v>1864450.28</v>
+        <v>1706297.81</v>
       </c>
       <c r="D14" t="n">
-        <v>24.61</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="15">
@@ -1006,13 +1006,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="n">
-        <v>58781</v>
+        <v>57255</v>
       </c>
       <c r="C15" t="n">
-        <v>1545059.56</v>
+        <v>1436910.73</v>
       </c>
       <c r="D15" t="n">
-        <v>26.29</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="16">
@@ -1020,13 +1020,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="n">
-        <v>61231</v>
+        <v>59653</v>
       </c>
       <c r="C16" t="n">
-        <v>1667226.99</v>
+        <v>1531974.62</v>
       </c>
       <c r="D16" t="n">
-        <v>27.23</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="17">
@@ -1034,13 +1034,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="n">
-        <v>78193</v>
+        <v>76823</v>
       </c>
       <c r="C17" t="n">
-        <v>1829718.02</v>
+        <v>1724049.58</v>
       </c>
       <c r="D17" t="n">
-        <v>23.4</v>
+        <v>22.44</v>
       </c>
     </row>
     <row r="18">
@@ -1048,13 +1048,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="n">
-        <v>87657</v>
+        <v>85602</v>
       </c>
       <c r="C18" t="n">
-        <v>2094361.09</v>
+        <v>1941937.59</v>
       </c>
       <c r="D18" t="n">
-        <v>23.89</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="19">
@@ -1062,13 +1062,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="n">
-        <v>35571</v>
+        <v>34509</v>
       </c>
       <c r="C19" t="n">
-        <v>1131455.38</v>
+        <v>1022961.46</v>
       </c>
       <c r="D19" t="n">
-        <v>31.81</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="20">
@@ -1076,13 +1076,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="n">
-        <v>88482</v>
+        <v>87438</v>
       </c>
       <c r="C20" t="n">
-        <v>1987961.98</v>
+        <v>1910879.13</v>
       </c>
       <c r="D20" t="n">
-        <v>22.47</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="21">
@@ -1090,13 +1090,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="n">
-        <v>70523</v>
+        <v>69928</v>
       </c>
       <c r="C21" t="n">
-        <v>1545155.28</v>
+        <v>1512346.08</v>
       </c>
       <c r="D21" t="n">
-        <v>21.91</v>
+        <v>21.63</v>
       </c>
     </row>
     <row r="22">
@@ -1104,13 +1104,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="n">
-        <v>56672</v>
+        <v>56256</v>
       </c>
       <c r="C22" t="n">
-        <v>1370926.25</v>
+        <v>1345848.21</v>
       </c>
       <c r="D22" t="n">
-        <v>24.19</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="23">
@@ -1118,13 +1118,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="n">
-        <v>81699</v>
+        <v>81061</v>
       </c>
       <c r="C23" t="n">
-        <v>1776622.47</v>
+        <v>1743438.98</v>
       </c>
       <c r="D23" t="n">
-        <v>21.75</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="24">
@@ -1132,13 +1132,13 @@
         <v>26</v>
       </c>
       <c r="B24" t="n">
-        <v>81709</v>
+        <v>80994</v>
       </c>
       <c r="C24" t="n">
-        <v>1817410.11</v>
+        <v>1773064.15</v>
       </c>
       <c r="D24" t="n">
-        <v>22.24</v>
+        <v>21.89</v>
       </c>
     </row>
     <row r="25">
@@ -1146,13 +1146,13 @@
         <v>27</v>
       </c>
       <c r="B25" t="n">
-        <v>77631</v>
+        <v>77087</v>
       </c>
       <c r="C25" t="n">
-        <v>1741025.44</v>
+        <v>1707556.19</v>
       </c>
       <c r="D25" t="n">
-        <v>22.43</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="26">
@@ -1160,13 +1160,13 @@
         <v>28</v>
       </c>
       <c r="B26" t="n">
-        <v>74525</v>
+        <v>74081</v>
       </c>
       <c r="C26" t="n">
-        <v>1677747.75</v>
+        <v>1656066.36</v>
       </c>
       <c r="D26" t="n">
-        <v>22.51</v>
+        <v>22.35</v>
       </c>
     </row>
   </sheetData>
@@ -1199,13 +1199,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>22197</v>
+        <v>20806</v>
       </c>
       <c r="C2" t="n">
-        <v>391323.81</v>
+        <v>344221.98</v>
       </c>
       <c r="D2" t="n">
-        <v>17.63</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="3">
@@ -1213,13 +1213,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>18079</v>
+        <v>17407</v>
       </c>
       <c r="C3" t="n">
-        <v>302438.04</v>
+        <v>277303.04</v>
       </c>
       <c r="D3" t="n">
-        <v>16.73</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="4">
@@ -1227,13 +1227,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>23016</v>
+        <v>21676</v>
       </c>
       <c r="C4" t="n">
-        <v>414260.09</v>
+        <v>351906.45</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="5">
@@ -1241,13 +1241,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>32143</v>
+        <v>30800</v>
       </c>
       <c r="C5" t="n">
-        <v>563552.21</v>
+        <v>482298.58</v>
       </c>
       <c r="D5" t="n">
-        <v>17.53</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="6">
@@ -1255,13 +1255,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>29931</v>
+        <v>28909</v>
       </c>
       <c r="C6" t="n">
-        <v>523662.58</v>
+        <v>460860.04</v>
       </c>
       <c r="D6" t="n">
-        <v>17.5</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="7">
@@ -1269,13 +1269,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>34939</v>
+        <v>33913</v>
       </c>
       <c r="C7" t="n">
-        <v>530723.58</v>
+        <v>471658.01</v>
       </c>
       <c r="D7" t="n">
-        <v>15.19</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="8">
@@ -1283,13 +1283,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>38965</v>
+        <v>37403</v>
       </c>
       <c r="C8" t="n">
-        <v>629140.71</v>
+        <v>543590.25</v>
       </c>
       <c r="D8" t="n">
-        <v>16.15</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="9">
@@ -1297,13 +1297,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>21296</v>
+        <v>20737</v>
       </c>
       <c r="C9" t="n">
-        <v>282454.16</v>
+        <v>255629.53</v>
       </c>
       <c r="D9" t="n">
-        <v>13.26</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="10">
@@ -1311,13 +1311,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>21811</v>
+        <v>21321</v>
       </c>
       <c r="C10" t="n">
-        <v>294880.78</v>
+        <v>267173.48</v>
       </c>
       <c r="D10" t="n">
-        <v>13.52</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="11">
@@ -1325,13 +1325,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>28899</v>
+        <v>28410</v>
       </c>
       <c r="C11" t="n">
-        <v>382002.05</v>
+        <v>355824.5</v>
       </c>
       <c r="D11" t="n">
-        <v>13.22</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="12">
@@ -1339,13 +1339,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>28999</v>
+        <v>28509</v>
       </c>
       <c r="C12" t="n">
-        <v>383376.58</v>
+        <v>356453.89</v>
       </c>
       <c r="D12" t="n">
-        <v>13.22</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13">
@@ -1353,13 +1353,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="n">
-        <v>27762</v>
+        <v>27710</v>
       </c>
       <c r="C13" t="n">
-        <v>332330.43</v>
+        <v>332328.48</v>
       </c>
       <c r="D13" t="n">
-        <v>11.97</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="14">
@@ -1367,13 +1367,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="n">
-        <v>26039</v>
+        <v>25527</v>
       </c>
       <c r="C14" t="n">
-        <v>348019.97</v>
+        <v>318379.63</v>
       </c>
       <c r="D14" t="n">
-        <v>13.37</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="15">
@@ -1381,13 +1381,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="n">
-        <v>20312</v>
+        <v>19871</v>
       </c>
       <c r="C15" t="n">
-        <v>255870.75</v>
+        <v>231926.64</v>
       </c>
       <c r="D15" t="n">
-        <v>12.6</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="16">
@@ -1395,13 +1395,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="n">
-        <v>21256</v>
+        <v>20710</v>
       </c>
       <c r="C16" t="n">
-        <v>280680.97</v>
+        <v>253103.8</v>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="17">
@@ -1409,13 +1409,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="n">
-        <v>30293</v>
+        <v>29786</v>
       </c>
       <c r="C17" t="n">
-        <v>402990.03</v>
+        <v>374751</v>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="18">
@@ -1423,13 +1423,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="n">
-        <v>30787</v>
+        <v>30308</v>
       </c>
       <c r="C18" t="n">
-        <v>403244.01</v>
+        <v>376510.36</v>
       </c>
       <c r="D18" t="n">
-        <v>13.1</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="19">
@@ -1437,13 +1437,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="n">
-        <v>26222</v>
+        <v>25878</v>
       </c>
       <c r="C19" t="n">
-        <v>307335.3</v>
+        <v>293463.24</v>
       </c>
       <c r="D19" t="n">
-        <v>11.72</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="20">
@@ -1451,13 +1451,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="n">
-        <v>29145</v>
+        <v>28830</v>
       </c>
       <c r="C20" t="n">
-        <v>341903.09</v>
+        <v>330290.61</v>
       </c>
       <c r="D20" t="n">
-        <v>11.73</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="21">
@@ -1465,13 +1465,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="n">
-        <v>21223</v>
+        <v>21091</v>
       </c>
       <c r="C21" t="n">
-        <v>233548.18</v>
+        <v>227824.08</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="22">
@@ -1479,13 +1479,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="n">
-        <v>18645</v>
+        <v>18522</v>
       </c>
       <c r="C22" t="n">
-        <v>208746.44</v>
+        <v>206066.69</v>
       </c>
       <c r="D22" t="n">
-        <v>11.2</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="23">
@@ -1493,13 +1493,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="n">
-        <v>28760</v>
+        <v>28192</v>
       </c>
       <c r="C23" t="n">
-        <v>334710.36</v>
+        <v>328750.42</v>
       </c>
       <c r="D23" t="n">
-        <v>11.64</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="24">
@@ -1507,13 +1507,13 @@
         <v>26</v>
       </c>
       <c r="B24" t="n">
-        <v>14121</v>
+        <v>13596</v>
       </c>
       <c r="C24" t="n">
-        <v>161012.04</v>
+        <v>155813.16</v>
       </c>
       <c r="D24" t="n">
-        <v>11.4</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="25">
@@ -1521,13 +1521,13 @@
         <v>27</v>
       </c>
       <c r="B25" t="n">
-        <v>8336</v>
+        <v>7720</v>
       </c>
       <c r="C25" t="n">
-        <v>78962.74</v>
+        <v>71403.83</v>
       </c>
       <c r="D25" t="n">
-        <v>9.47</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="26">
@@ -1535,13 +1535,13 @@
         <v>28</v>
       </c>
       <c r="B26" t="n">
-        <v>6904</v>
+        <v>6371</v>
       </c>
       <c r="C26" t="n">
-        <v>58027.87</v>
+        <v>51743.7</v>
       </c>
       <c r="D26" t="n">
-        <v>8.4</v>
+        <v>8.12</v>
       </c>
     </row>
   </sheetData>
@@ -1574,13 +1574,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>11390</v>
+        <v>10933</v>
       </c>
       <c r="C2" t="n">
-        <v>87372.71</v>
+        <v>87366.29</v>
       </c>
       <c r="D2" t="n">
-        <v>7.67</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="3">
@@ -1588,13 +1588,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>11343</v>
+        <v>11148</v>
       </c>
       <c r="C3" t="n">
-        <v>90402.24</v>
+        <v>90398.88</v>
       </c>
       <c r="D3" t="n">
-        <v>7.97</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="4">
@@ -1602,13 +1602,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>14507</v>
+        <v>14233</v>
       </c>
       <c r="C4" t="n">
-        <v>116593.69</v>
+        <v>116580.72</v>
       </c>
       <c r="D4" t="n">
-        <v>8.04</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="5">
@@ -1616,13 +1616,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>13915</v>
+        <v>13117</v>
       </c>
       <c r="C5" t="n">
         <v>104132.05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.48</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="6">
@@ -1630,13 +1630,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>12989</v>
+        <v>12300</v>
       </c>
       <c r="C6" t="n">
         <v>95940.41</v>
       </c>
       <c r="D6" t="n">
-        <v>7.39</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7">
@@ -1644,13 +1644,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>15459</v>
+        <v>14552</v>
       </c>
       <c r="C7" t="n">
         <v>108075.84</v>
       </c>
       <c r="D7" t="n">
-        <v>6.99</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="8">
@@ -1658,13 +1658,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>13546</v>
+        <v>11865</v>
       </c>
       <c r="C8" t="n">
-        <v>88650.09</v>
+        <v>85537.31</v>
       </c>
       <c r="D8" t="n">
-        <v>6.54</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="9">
@@ -1672,13 +1672,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>10807</v>
+        <v>9823</v>
       </c>
       <c r="C9" t="n">
-        <v>71912.05</v>
+        <v>70441.25</v>
       </c>
       <c r="D9" t="n">
-        <v>6.65</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="10">
@@ -1686,13 +1686,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>9960</v>
+        <v>8987</v>
       </c>
       <c r="C10" t="n">
-        <v>67394.43</v>
+        <v>65778.62</v>
       </c>
       <c r="D10" t="n">
-        <v>6.77</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="11">
@@ -1700,13 +1700,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>12037</v>
+        <v>10366</v>
       </c>
       <c r="C11" t="n">
-        <v>80287.99</v>
+        <v>77245.09</v>
       </c>
       <c r="D11" t="n">
-        <v>6.67</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="12">
@@ -1714,13 +1714,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>14114</v>
+        <v>12705</v>
       </c>
       <c r="C12" t="n">
-        <v>101200.09</v>
+        <v>98620.15</v>
       </c>
       <c r="D12" t="n">
-        <v>7.17</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="13">
@@ -1728,13 +1728,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="n">
-        <v>14615</v>
+        <v>13181</v>
       </c>
       <c r="C13" t="n">
-        <v>105998.19</v>
+        <v>102741.64</v>
       </c>
       <c r="D13" t="n">
-        <v>7.25</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="14">
@@ -1742,13 +1742,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="n">
-        <v>14883</v>
+        <v>13507</v>
       </c>
       <c r="C14" t="n">
-        <v>110453.62</v>
+        <v>107320.55</v>
       </c>
       <c r="D14" t="n">
-        <v>7.42</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="15">
@@ -1756,13 +1756,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="n">
-        <v>12627</v>
+        <v>12108</v>
       </c>
       <c r="C15" t="n">
-        <v>97062.73</v>
+        <v>97059.37</v>
       </c>
       <c r="D15" t="n">
-        <v>7.69</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="16">
@@ -1770,13 +1770,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="n">
-        <v>14053</v>
+        <v>13665</v>
       </c>
       <c r="C16" t="n">
-        <v>110842.68</v>
+        <v>110829.72</v>
       </c>
       <c r="D16" t="n">
-        <v>7.89</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="17">
@@ -1784,13 +1784,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="n">
-        <v>11218</v>
+        <v>10423</v>
       </c>
       <c r="C17" t="n">
-        <v>83033.42</v>
+        <v>81911.27</v>
       </c>
       <c r="D17" t="n">
-        <v>7.4</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="18">
@@ -1798,13 +1798,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="n">
-        <v>13730</v>
+        <v>12610</v>
       </c>
       <c r="C18" t="n">
-        <v>100136.89</v>
+        <v>98110.64</v>
       </c>
       <c r="D18" t="n">
-        <v>7.29</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="19">
@@ -1812,13 +1812,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="n">
-        <v>11433</v>
+        <v>11150</v>
       </c>
       <c r="C19" t="n">
         <v>84203.19</v>
       </c>
       <c r="D19" t="n">
-        <v>7.36</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="20">
@@ -1826,13 +1826,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="n">
-        <v>13272</v>
+        <v>12962</v>
       </c>
       <c r="C20" t="n">
         <v>93851.24</v>
       </c>
       <c r="D20" t="n">
-        <v>7.07</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="21">
@@ -1840,13 +1840,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="n">
-        <v>11423</v>
+        <v>11055</v>
       </c>
       <c r="C21" t="n">
         <v>80611.89</v>
       </c>
       <c r="D21" t="n">
-        <v>7.06</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="22">
@@ -1854,13 +1854,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="n">
-        <v>10483</v>
+        <v>10304</v>
       </c>
       <c r="C22" t="n">
         <v>78091.09</v>
       </c>
       <c r="D22" t="n">
-        <v>7.45</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="23">
@@ -1868,13 +1868,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="n">
-        <v>12073</v>
+        <v>11742</v>
       </c>
       <c r="C23" t="n">
         <v>88079.22</v>
       </c>
       <c r="D23" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="24">
@@ -1882,13 +1882,13 @@
         <v>26</v>
       </c>
       <c r="B24" t="n">
-        <v>12648</v>
+        <v>12328</v>
       </c>
       <c r="C24" t="n">
         <v>97749.22</v>
       </c>
       <c r="D24" t="n">
-        <v>7.73</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="25">
@@ -1896,13 +1896,13 @@
         <v>27</v>
       </c>
       <c r="B25" t="n">
-        <v>16134</v>
+        <v>15752</v>
       </c>
       <c r="C25" t="n">
         <v>123726.6</v>
       </c>
       <c r="D25" t="n">
-        <v>7.67</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="26">
@@ -1910,13 +1910,13 @@
         <v>28</v>
       </c>
       <c r="B26" t="n">
-        <v>13533</v>
+        <v>13127</v>
       </c>
       <c r="C26" t="n">
         <v>104030.15</v>
       </c>
       <c r="D26" t="n">
-        <v>7.69</v>
+        <v>7.92</v>
       </c>
     </row>
   </sheetData>
